--- a/1_Data/Wozniak_2020_PLOS/Exp3/Codebook_Wozniak_2020_PLOS_Exp3_Clean.xlsx
+++ b/1_Data/Wozniak_2020_PLOS/Exp3/Codebook_Wozniak_2020_PLOS_Exp3_Clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,17 +551,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matching</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Whether the cue-target pairing matched the learned associations</t>
+          <t>Task type: the kind of shape-label matching task performed in the trial (default self-matching; other tasks e.g. facialExpression-matching, monetaryValue-matching, self-pseudoWords)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Matching; Nonmatching</t>
+          <t>self-matching</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,17 +573,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Label_Origin_Identity</t>
+          <t>Matching</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verbatim label text (same as Label)</t>
+          <t>Whether the cue-target pairing matched the learned associations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Liz; Meg; Pam; Rob; Sam; You</t>
+          <t>Matching; Nonmatching</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Label_English_Identity</t>
+          <t>Label_Origin_Identity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>English semantic description of the label identity (per experiment: Exp1 You=Self label, others=Stranger names; Exp2 own-face name=Own-face name; Exp3 You=Self label (You), own-face name=Own-face name)</t>
+          <t>Verbatim label text (same as Label)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Own-face name; Self label (You); Stranger name</t>
+          <t>Liz; Meg; Pam; Rob; Sam; You</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,17 +617,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Label_Standardized_Identity</t>
+          <t>Label_English_Identity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Standardized identity of the label (6-category vocabulary)</t>
+          <t>English semantic description of the label identity (per experiment: Exp1 You=Self label, others=Stranger names; Exp2 own-face name=Own-face name; Exp3 You=Self label (You), own-face name=Own-face name)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Self; Stranger</t>
+          <t>Own-face name; Self label (You); Stranger name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -639,17 +639,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shape_Origin_Identity</t>
+          <t>Label_Standardized_Identity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Author internal identity code of the target face (You/Neutral/AntiYou; per-subject assignment from raw columns 17-19; semantics per experiment: Exp1 You=Self-associated stranger face, Neutral/AntiYou=Stranger faces; Exp2 AntiYou=own face, You/Neutral=Stranger faces; Exp3 You=self-associated stranger face, AntiYou=own face, Neutral=Stranger face)</t>
+          <t>Standardized identity of the label (6-category vocabulary)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>You; Neutral; AntiYou</t>
+          <t>Self; Stranger</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -661,17 +661,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shape_English_Identity</t>
+          <t>Shape_Origin_Identity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>English semantic description of the target face identity (Self-associated face = arbitrarily associated with self; Own face = participant real face; Stranger face)</t>
+          <t>Author internal identity code of the target face (You/Neutral/AntiYou; per-subject assignment from raw columns 17-19; semantics per experiment: Exp1 You=Self-associated stranger face, Neutral/AntiYou=Stranger faces; Exp2 AntiYou=own face, You/Neutral=Stranger faces; Exp3 You=self-associated stranger face, AntiYou=own face, Neutral=Stranger face)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Own face; Self-associated face; Stranger face</t>
+          <t>You; Neutral; AntiYou</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -683,17 +683,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shape_Standardized_Identity</t>
+          <t>Shape_English_Identity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Standardized identity of the target face (6-category vocabulary)</t>
+          <t>English semantic description of the target face identity (Self-associated face = arbitrarily associated with self; Own face = participant real face; Stranger face)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Self; Stranger</t>
+          <t>Own face; Self-associated face; Stranger face</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,39 +705,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RT_ms</t>
+          <t>Shape_Standardized_Identity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reaction time in milliseconds (from face onset to keypress); NA for no-response trials (raw pseudo-value ~2000 ms kept in *_raw.csv)</t>
+          <t>Standardized identity of the target face (6-category vocabulary)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ms; NA (no response)</t>
+          <t>Self; Stranger</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RT_sec</t>
+          <t>RT_ms</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reaction time in seconds (RT_ms/1000); NA for no-response</t>
+          <t>Reaction time in milliseconds (from face onset to keypress); NA for no-response trials (raw pseudo-value ~2000 ms kept in *_raw.csv)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>s; NA (no response)</t>
+          <t>ms; NA (no response)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -749,20 +749,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>RT_sec</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Reaction time in seconds (RT_ms/1000); NA for no-response</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>s; NA (no response)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Accuracy: 1 = correct key for the pairing type, 0 = wrong key within response window, NA = no response (key x)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>1 (correct); 0 (incorrect); NA (no response)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Categorical</t>
         </is>
